--- a/uploads/excel/new_WO_Header_Status_-_Labor_Vendor_Updated_Open_WO_ONLY_7-7-2026_4-47-39_PM.xlsx
+++ b/uploads/excel/new_WO_Header_Status_-_Labor_Vendor_Updated_Open_WO_ONLY_7-7-2026_4-47-39_PM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DEVILISTIAWATI\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mifta\Desktop\devi\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_86774BBDDB6893C8D4F034C7DE25337EE45B802F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3120" windowWidth="51600" windowHeight="16725" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="_new_ WO Header Status - La..." sheetId="1" r:id="rId1"/>
@@ -9142,7 +9142,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="dataSheet"/>
   <dimension ref="A1:AS207"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="0" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="0" style="1" hidden="1" customWidth="1"/>
@@ -9300,7 +9300,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:45" ht="71.25">
+    <row r="2" spans="1:45" ht="75">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -9419,7 +9419,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:45" ht="42.75">
+    <row r="3" spans="1:45" ht="45">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -9535,7 +9535,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:45" ht="42.75">
+    <row r="4" spans="1:45" ht="60">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -9651,7 +9651,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:45" ht="57">
+    <row r="5" spans="1:45" ht="60">
       <c r="A5" t="s">
         <v>109</v>
       </c>
@@ -9767,7 +9767,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:45" ht="42.75">
+    <row r="6" spans="1:45" ht="45">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -9883,7 +9883,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:45" ht="71.25">
+    <row r="7" spans="1:45" ht="90">
       <c r="A7" t="s">
         <v>140</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:45" ht="57">
+    <row r="8" spans="1:45" ht="60">
       <c r="A8" t="s">
         <v>156</v>
       </c>
@@ -10115,7 +10115,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:45" ht="57">
+    <row r="9" spans="1:45" ht="75">
       <c r="A9" t="s">
         <v>173</v>
       </c>
@@ -10231,7 +10231,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:45" ht="57">
+    <row r="10" spans="1:45" ht="60">
       <c r="A10" t="s">
         <v>186</v>
       </c>
@@ -10347,7 +10347,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:45" ht="42.75">
+    <row r="11" spans="1:45" ht="60">
       <c r="A11" t="s">
         <v>202</v>
       </c>
@@ -10463,7 +10463,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:45" ht="42.75">
+    <row r="12" spans="1:45" ht="45">
       <c r="A12" t="s">
         <v>217</v>
       </c>
@@ -10579,7 +10579,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:45" ht="42.75">
+    <row r="13" spans="1:45" ht="45">
       <c r="A13" t="s">
         <v>229</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:45" ht="57">
+    <row r="14" spans="1:45" ht="60">
       <c r="A14" t="s">
         <v>244</v>
       </c>
@@ -10814,7 +10814,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:45" ht="57">
+    <row r="15" spans="1:45" ht="60">
       <c r="A15" t="s">
         <v>257</v>
       </c>
@@ -10930,7 +10930,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:45" ht="42.75">
+    <row r="16" spans="1:45" ht="45">
       <c r="A16" t="s">
         <v>274</v>
       </c>
@@ -11046,7 +11046,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:45" ht="42.75">
+    <row r="17" spans="1:45" ht="60">
       <c r="A17" t="s">
         <v>288</v>
       </c>
@@ -11165,7 +11165,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:45" ht="57">
+    <row r="18" spans="1:45" ht="60">
       <c r="A18" t="s">
         <v>306</v>
       </c>
@@ -11284,7 +11284,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="19" spans="1:45" ht="57">
+    <row r="19" spans="1:45" ht="75">
       <c r="A19" t="s">
         <v>325</v>
       </c>
@@ -11403,7 +11403,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="20" spans="1:45" ht="57">
+    <row r="20" spans="1:45" ht="60">
       <c r="A20" t="s">
         <v>340</v>
       </c>
@@ -11519,7 +11519,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:45" ht="85.5">
+    <row r="21" spans="1:45" ht="90">
       <c r="A21" t="s">
         <v>355</v>
       </c>
@@ -11635,7 +11635,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:45" ht="42.75">
+    <row r="22" spans="1:45" ht="45">
       <c r="A22" t="s">
         <v>371</v>
       </c>
@@ -11751,7 +11751,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:45" ht="57">
+    <row r="23" spans="1:45" ht="60">
       <c r="A23" t="s">
         <v>383</v>
       </c>
@@ -11867,7 +11867,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:45" ht="71.25">
+    <row r="24" spans="1:45" ht="75">
       <c r="A24" t="s">
         <v>396</v>
       </c>
@@ -11983,7 +11983,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:45" ht="57">
+    <row r="25" spans="1:45" ht="60">
       <c r="A25" t="s">
         <v>405</v>
       </c>
@@ -12105,7 +12105,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="26" spans="1:45" ht="71.25">
+    <row r="26" spans="1:45" ht="75">
       <c r="A26" t="s">
         <v>420</v>
       </c>
@@ -12221,7 +12221,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:45" ht="71.25">
+    <row r="27" spans="1:45" ht="75">
       <c r="A27" t="s">
         <v>433</v>
       </c>
@@ -12337,7 +12337,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:45" ht="71.25">
+    <row r="28" spans="1:45" ht="75">
       <c r="A28" t="s">
         <v>448</v>
       </c>
@@ -12459,7 +12459,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:45" ht="71.25">
+    <row r="29" spans="1:45" ht="75">
       <c r="A29" t="s">
         <v>460</v>
       </c>
@@ -12578,7 +12578,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="30" spans="1:45" ht="42.75">
+    <row r="30" spans="1:45" ht="60">
       <c r="A30" t="s">
         <v>474</v>
       </c>
@@ -12697,7 +12697,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="31" spans="1:45" ht="71.25">
+    <row r="31" spans="1:45" ht="105">
       <c r="A31" t="s">
         <v>484</v>
       </c>
@@ -12819,7 +12819,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="32" spans="1:45" ht="42.75">
+    <row r="32" spans="1:45" ht="45">
       <c r="A32" t="s">
         <v>497</v>
       </c>
@@ -12941,7 +12941,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="33" spans="1:45" ht="57">
+    <row r="33" spans="1:45" ht="60">
       <c r="A33" t="s">
         <v>511</v>
       </c>
@@ -13063,7 +13063,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="34" spans="1:45" ht="42.75">
+    <row r="34" spans="1:45" ht="45">
       <c r="A34" t="s">
         <v>527</v>
       </c>
@@ -13185,7 +13185,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="35" spans="1:45" ht="28.5">
+    <row r="35" spans="1:45" ht="30">
       <c r="A35" t="s">
         <v>540</v>
       </c>
@@ -13301,7 +13301,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:45" ht="57">
+    <row r="36" spans="1:45" ht="60">
       <c r="A36" t="s">
         <v>552</v>
       </c>
@@ -13426,7 +13426,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:45" ht="28.5">
+    <row r="37" spans="1:45" ht="45">
       <c r="A37" t="s">
         <v>565</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:45" ht="57">
+    <row r="38" spans="1:45" ht="75">
       <c r="A38" t="s">
         <v>575</v>
       </c>
@@ -13661,7 +13661,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:45" ht="71.25">
+    <row r="39" spans="1:45" ht="75">
       <c r="A39" t="s">
         <v>588</v>
       </c>
@@ -13780,7 +13780,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="40" spans="1:45" ht="42.75">
+    <row r="40" spans="1:45" ht="60">
       <c r="A40" t="s">
         <v>600</v>
       </c>
@@ -13896,7 +13896,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:45" ht="57">
+    <row r="41" spans="1:45" ht="75">
       <c r="A41" t="s">
         <v>613</v>
       </c>
@@ -14015,7 +14015,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:45" ht="42.75">
+    <row r="42" spans="1:45" ht="60">
       <c r="A42" t="s">
         <v>625</v>
       </c>
@@ -14131,7 +14131,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:45" ht="42.75">
+    <row r="43" spans="1:45" ht="45">
       <c r="A43" t="s">
         <v>639</v>
       </c>
@@ -14247,7 +14247,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:45" ht="42.75">
+    <row r="44" spans="1:45" ht="60">
       <c r="A44" t="s">
         <v>651</v>
       </c>
@@ -14363,7 +14363,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:45" ht="71.25">
+    <row r="45" spans="1:45" ht="90">
       <c r="A45" t="s">
         <v>667</v>
       </c>
@@ -14479,7 +14479,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:45" ht="42.75">
+    <row r="46" spans="1:45" ht="45">
       <c r="A46" t="s">
         <v>680</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="1:45" ht="71.25">
+    <row r="47" spans="1:45" ht="90">
       <c r="A47" t="s">
         <v>693</v>
       </c>
@@ -14714,7 +14714,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:45" ht="71.25">
+    <row r="48" spans="1:45" ht="90">
       <c r="A48" t="s">
         <v>704</v>
       </c>
@@ -14830,7 +14830,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:45" ht="71.25">
+    <row r="49" spans="1:45" ht="75">
       <c r="A49" t="s">
         <v>718</v>
       </c>
@@ -14952,7 +14952,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:45" ht="42.75">
+    <row r="50" spans="1:45" ht="45">
       <c r="A50" t="s">
         <v>731</v>
       </c>
@@ -15074,7 +15074,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:45" ht="28.5">
+    <row r="51" spans="1:45" ht="45">
       <c r="A51" t="s">
         <v>743</v>
       </c>
@@ -15193,7 +15193,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="1:45" ht="42.75">
+    <row r="52" spans="1:45" ht="45">
       <c r="A52" t="s">
         <v>755</v>
       </c>
@@ -15315,7 +15315,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:45" ht="71.25">
+    <row r="53" spans="1:45" ht="90">
       <c r="A53" t="s">
         <v>766</v>
       </c>
@@ -15434,7 +15434,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="1:45" ht="57">
+    <row r="54" spans="1:45" ht="60">
       <c r="A54" t="s">
         <v>773</v>
       </c>
@@ -15553,7 +15553,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="55" spans="1:45" ht="57">
+    <row r="55" spans="1:45" ht="75">
       <c r="A55" t="s">
         <v>786</v>
       </c>
@@ -15675,7 +15675,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:45" ht="71.25">
+    <row r="56" spans="1:45" ht="75">
       <c r="A56" t="s">
         <v>798</v>
       </c>
@@ -15794,7 +15794,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="57" spans="1:45" ht="71.25">
+    <row r="57" spans="1:45" ht="75">
       <c r="A57" t="s">
         <v>815</v>
       </c>
@@ -15913,7 +15913,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="58" spans="1:45" ht="42.75">
+    <row r="58" spans="1:45" ht="45">
       <c r="A58" t="s">
         <v>829</v>
       </c>
@@ -16032,7 +16032,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:45" ht="57">
+    <row r="59" spans="1:45" ht="75">
       <c r="A59" t="s">
         <v>841</v>
       </c>
@@ -16157,7 +16157,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="60" spans="1:45" ht="42.75">
+    <row r="60" spans="1:45" ht="45">
       <c r="A60" t="s">
         <v>854</v>
       </c>
@@ -16273,7 +16273,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="61" spans="1:45" ht="42.75">
+    <row r="61" spans="1:45" ht="45">
       <c r="A61" t="s">
         <v>869</v>
       </c>
@@ -16398,7 +16398,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="62" spans="1:45" ht="57">
+    <row r="62" spans="1:45" ht="60">
       <c r="A62" t="s">
         <v>880</v>
       </c>
@@ -16517,7 +16517,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="63" spans="1:45" ht="57">
+    <row r="63" spans="1:45" ht="75">
       <c r="A63" t="s">
         <v>894</v>
       </c>
@@ -16642,7 +16642,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="64" spans="1:45" ht="57">
+    <row r="64" spans="1:45" ht="60">
       <c r="A64" t="s">
         <v>907</v>
       </c>
@@ -16758,7 +16758,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="65" spans="1:44" ht="71.25">
+    <row r="65" spans="1:44" ht="90">
       <c r="A65" t="s">
         <v>918</v>
       </c>
@@ -16874,7 +16874,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="66" spans="1:44" ht="85.5">
+    <row r="66" spans="1:44" ht="90">
       <c r="A66" t="s">
         <v>931</v>
       </c>
@@ -16990,7 +16990,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="1:44" ht="42.75">
+    <row r="67" spans="1:44" ht="60">
       <c r="A67" t="s">
         <v>944</v>
       </c>
@@ -17109,7 +17109,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="1:44" ht="57">
+    <row r="68" spans="1:44" ht="60">
       <c r="A68" t="s">
         <v>955</v>
       </c>
@@ -17225,7 +17225,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="1:44" ht="28.5">
+    <row r="69" spans="1:44" ht="30">
       <c r="A69" t="s">
         <v>968</v>
       </c>
@@ -17347,7 +17347,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:44" ht="42.75">
+    <row r="70" spans="1:44" ht="45">
       <c r="A70" t="s">
         <v>981</v>
       </c>
@@ -17463,7 +17463,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="71" spans="1:44" ht="71.25">
+    <row r="71" spans="1:44" ht="90">
       <c r="A71" t="s">
         <v>992</v>
       </c>
@@ -17588,7 +17588,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="72" spans="1:44" ht="42.75">
+    <row r="72" spans="1:44" ht="45">
       <c r="A72" t="s">
         <v>1005</v>
       </c>
@@ -17707,7 +17707,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="73" spans="1:44" ht="42.75">
+    <row r="73" spans="1:44" ht="45">
       <c r="A73" t="s">
         <v>1018</v>
       </c>
@@ -17823,7 +17823,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="74" spans="1:44" ht="28.5">
+    <row r="74" spans="1:44" ht="30">
       <c r="A74" t="s">
         <v>1030</v>
       </c>
@@ -17942,7 +17942,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="75" spans="1:44" ht="42.75">
+    <row r="75" spans="1:44" ht="45">
       <c r="A75" t="s">
         <v>1043</v>
       </c>
@@ -18064,7 +18064,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="76" spans="1:44" ht="99.75">
+    <row r="76" spans="1:44" ht="105">
       <c r="A76" t="s">
         <v>1055</v>
       </c>
@@ -18186,7 +18186,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="77" spans="1:44" ht="57">
+    <row r="77" spans="1:44" ht="60">
       <c r="A77" t="s">
         <v>1066</v>
       </c>
@@ -18305,7 +18305,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="78" spans="1:44" ht="42.75">
+    <row r="78" spans="1:44" ht="45">
       <c r="A78" t="s">
         <v>1077</v>
       </c>
@@ -18421,7 +18421,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="79" spans="1:44" ht="57">
+    <row r="79" spans="1:44" ht="60">
       <c r="A79" t="s">
         <v>1087</v>
       </c>
@@ -18537,7 +18537,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="80" spans="1:44" ht="42.75">
+    <row r="80" spans="1:44" ht="45">
       <c r="A80" t="s">
         <v>1100</v>
       </c>
@@ -18659,7 +18659,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="81" spans="1:45" ht="57">
+    <row r="81" spans="1:45" ht="60">
       <c r="A81" t="s">
         <v>1111</v>
       </c>
@@ -18778,7 +18778,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="82" spans="1:45" ht="57">
+    <row r="82" spans="1:45" ht="75">
       <c r="A82" t="s">
         <v>1122</v>
       </c>
@@ -18894,7 +18894,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="83" spans="1:45" ht="57">
+    <row r="83" spans="1:45" ht="60">
       <c r="A83" t="s">
         <v>1132</v>
       </c>
@@ -19016,7 +19016,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:45" ht="57">
+    <row r="84" spans="1:45" ht="60">
       <c r="A84" t="s">
         <v>1142</v>
       </c>
@@ -19138,7 +19138,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="85" spans="1:45" ht="71.25">
+    <row r="85" spans="1:45" ht="90">
       <c r="A85" t="s">
         <v>1153</v>
       </c>
@@ -19260,7 +19260,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="86" spans="1:45" ht="42.75">
+    <row r="86" spans="1:45" ht="60">
       <c r="A86" t="s">
         <v>1164</v>
       </c>
@@ -19382,7 +19382,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="87" spans="1:45" ht="42.75">
+    <row r="87" spans="1:45" ht="45">
       <c r="A87" t="s">
         <v>1174</v>
       </c>
@@ -19501,7 +19501,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="88" spans="1:45" ht="71.25">
+    <row r="88" spans="1:45" ht="75">
       <c r="A88" t="s">
         <v>1184</v>
       </c>
@@ -19626,7 +19626,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="89" spans="1:45" ht="42.75">
+    <row r="89" spans="1:45" ht="45">
       <c r="A89" t="s">
         <v>1191</v>
       </c>
@@ -19742,7 +19742,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="90" spans="1:45" ht="42.75">
+    <row r="90" spans="1:45" ht="60">
       <c r="A90" t="s">
         <v>1202</v>
       </c>
@@ -19858,7 +19858,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="91" spans="1:45" ht="42.75">
+    <row r="91" spans="1:45" ht="45">
       <c r="A91" t="s">
         <v>1216</v>
       </c>
@@ -19974,7 +19974,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="92" spans="1:45" ht="42.75">
+    <row r="92" spans="1:45" ht="45">
       <c r="A92" t="s">
         <v>1226</v>
       </c>
@@ -20090,7 +20090,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="93" spans="1:45" ht="42.75">
+    <row r="93" spans="1:45" ht="75">
       <c r="A93" t="s">
         <v>1235</v>
       </c>
@@ -20212,7 +20212,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="94" spans="1:45" ht="57">
+    <row r="94" spans="1:45" ht="75">
       <c r="A94" t="s">
         <v>1246</v>
       </c>
@@ -20328,7 +20328,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="95" spans="1:45" ht="71.25">
+    <row r="95" spans="1:45" ht="75">
       <c r="A95" t="s">
         <v>1258</v>
       </c>
@@ -20447,7 +20447,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="96" spans="1:45" ht="28.5">
+    <row r="96" spans="1:45" ht="30">
       <c r="A96" t="s">
         <v>1269</v>
       </c>
@@ -20563,7 +20563,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="97" spans="1:45" ht="42.75">
+    <row r="97" spans="1:45" ht="60">
       <c r="A97" t="s">
         <v>1279</v>
       </c>
@@ -20682,7 +20682,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="98" spans="1:45" ht="28.5">
+    <row r="98" spans="1:45" ht="45">
       <c r="A98" t="s">
         <v>1291</v>
       </c>
@@ -20798,7 +20798,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="99" spans="1:45" ht="42.75">
+    <row r="99" spans="1:45" ht="60">
       <c r="A99" t="s">
         <v>1301</v>
       </c>
@@ -20917,7 +20917,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="100" spans="1:45" ht="28.5">
+    <row r="100" spans="1:45" ht="30">
       <c r="A100" t="s">
         <v>1312</v>
       </c>
@@ -21033,7 +21033,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="101" spans="1:45" ht="71.25">
+    <row r="101" spans="1:45" ht="75">
       <c r="A101" t="s">
         <v>1322</v>
       </c>
@@ -21155,7 +21155,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="102" spans="1:45" ht="42.75">
+    <row r="102" spans="1:45" ht="45">
       <c r="A102" t="s">
         <v>1334</v>
       </c>
@@ -21271,7 +21271,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="103" spans="1:45" ht="71.25">
+    <row r="103" spans="1:45" ht="75">
       <c r="A103" t="s">
         <v>1344</v>
       </c>
@@ -21390,7 +21390,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="104" spans="1:45" ht="57">
+    <row r="104" spans="1:45" ht="75">
       <c r="A104" t="s">
         <v>1355</v>
       </c>
@@ -21515,7 +21515,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="105" spans="1:45" ht="42.75">
+    <row r="105" spans="1:45" ht="45">
       <c r="A105" t="s">
         <v>1371</v>
       </c>
@@ -21634,7 +21634,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="106" spans="1:45" ht="57">
+    <row r="106" spans="1:45" ht="60">
       <c r="A106" t="s">
         <v>1383</v>
       </c>
@@ -21750,7 +21750,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="107" spans="1:45" ht="42.75">
+    <row r="107" spans="1:45" ht="45">
       <c r="A107" t="s">
         <v>1394</v>
       </c>
@@ -21866,7 +21866,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="108" spans="1:45" ht="42.75">
+    <row r="108" spans="1:45" ht="45">
       <c r="A108" t="s">
         <v>1403</v>
       </c>
@@ -21982,7 +21982,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="109" spans="1:45" ht="42.75">
+    <row r="109" spans="1:45" ht="60">
       <c r="A109" t="s">
         <v>1413</v>
       </c>
@@ -22104,7 +22104,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="110" spans="1:45" ht="57">
+    <row r="110" spans="1:45" ht="60">
       <c r="A110" t="s">
         <v>1423</v>
       </c>
@@ -22226,7 +22226,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="111" spans="1:45" ht="42.75">
+    <row r="111" spans="1:45" ht="45">
       <c r="A111" t="s">
         <v>1433</v>
       </c>
@@ -22342,7 +22342,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="112" spans="1:45" ht="42.75">
+    <row r="112" spans="1:45" ht="60">
       <c r="A112" t="s">
         <v>1444</v>
       </c>
@@ -22461,7 +22461,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="113" spans="1:45" ht="42.75">
+    <row r="113" spans="1:45" ht="45">
       <c r="A113" t="s">
         <v>1457</v>
       </c>
@@ -22580,7 +22580,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="114" spans="1:45" ht="71.25">
+    <row r="114" spans="1:45" ht="75">
       <c r="A114" t="s">
         <v>1469</v>
       </c>
@@ -22702,7 +22702,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="115" spans="1:45" ht="57">
+    <row r="115" spans="1:45" ht="60">
       <c r="A115" t="s">
         <v>1480</v>
       </c>
@@ -22821,7 +22821,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="116" spans="1:45" ht="57">
+    <row r="116" spans="1:45" ht="60">
       <c r="A116" t="s">
         <v>1493</v>
       </c>
@@ -22943,7 +22943,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="117" spans="1:45" ht="42.75">
+    <row r="117" spans="1:45" ht="45">
       <c r="A117" t="s">
         <v>1504</v>
       </c>
@@ -23059,7 +23059,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="118" spans="1:45" ht="42.75">
+    <row r="118" spans="1:45" ht="60">
       <c r="A118" t="s">
         <v>1514</v>
       </c>
@@ -23175,7 +23175,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="119" spans="1:45" ht="85.5">
+    <row r="119" spans="1:45" ht="105">
       <c r="A119" t="s">
         <v>1525</v>
       </c>
@@ -23291,7 +23291,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="120" spans="1:45" ht="42.75">
+    <row r="120" spans="1:45" ht="45">
       <c r="A120" t="s">
         <v>1538</v>
       </c>
@@ -23413,7 +23413,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="121" spans="1:45" ht="42.75">
+    <row r="121" spans="1:45" ht="45">
       <c r="A121" t="s">
         <v>1549</v>
       </c>
@@ -23529,7 +23529,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="122" spans="1:45" ht="42.75">
+    <row r="122" spans="1:45" ht="45">
       <c r="A122" t="s">
         <v>1560</v>
       </c>
@@ -23648,7 +23648,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="123" spans="1:45" ht="42.75">
+    <row r="123" spans="1:45" ht="60">
       <c r="A123" t="s">
         <v>1573</v>
       </c>
@@ -23770,7 +23770,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="124" spans="1:45" ht="42.75">
+    <row r="124" spans="1:45" ht="45">
       <c r="A124" t="s">
         <v>1584</v>
       </c>
@@ -23892,7 +23892,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="125" spans="1:45" ht="57">
+    <row r="125" spans="1:45" ht="75">
       <c r="A125" t="s">
         <v>1598</v>
       </c>
@@ -24014,7 +24014,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="126" spans="1:45" ht="42.75">
+    <row r="126" spans="1:45" ht="45">
       <c r="A126" t="s">
         <v>1611</v>
       </c>
@@ -24139,7 +24139,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="127" spans="1:45" ht="57">
+    <row r="127" spans="1:45" ht="75">
       <c r="A127" t="s">
         <v>1622</v>
       </c>
@@ -24264,7 +24264,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="128" spans="1:45" ht="57">
+    <row r="128" spans="1:45" ht="60">
       <c r="A128" t="s">
         <v>1636</v>
       </c>
@@ -24383,7 +24383,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="129" spans="1:45" ht="71.25">
+    <row r="129" spans="1:45" ht="90">
       <c r="A129" t="s">
         <v>1649</v>
       </c>
@@ -24505,7 +24505,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="130" spans="1:45" ht="71.25">
+    <row r="130" spans="1:45" ht="75">
       <c r="A130" t="s">
         <v>1661</v>
       </c>
@@ -24624,7 +24624,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="131" spans="1:45" ht="71.25">
+    <row r="131" spans="1:45" ht="75">
       <c r="A131" t="s">
         <v>1672</v>
       </c>
@@ -24749,7 +24749,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="132" spans="1:45" ht="57">
+    <row r="132" spans="1:45" ht="60">
       <c r="A132" t="s">
         <v>1681</v>
       </c>
@@ -24874,7 +24874,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="133" spans="1:45" ht="57">
+    <row r="133" spans="1:45" ht="60">
       <c r="A133" t="s">
         <v>1689</v>
       </c>
@@ -24990,7 +24990,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="134" spans="1:45" ht="28.5">
+    <row r="134" spans="1:45" ht="30">
       <c r="A134" t="s">
         <v>1698</v>
       </c>
@@ -25115,7 +25115,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="135" spans="1:45" ht="57">
+    <row r="135" spans="1:45" ht="60">
       <c r="A135" t="s">
         <v>1710</v>
       </c>
@@ -25234,7 +25234,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="136" spans="1:45" ht="57">
+    <row r="136" spans="1:45" ht="75">
       <c r="A136" t="s">
         <v>1721</v>
       </c>
@@ -25353,7 +25353,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="137" spans="1:45" ht="57">
+    <row r="137" spans="1:45" ht="60">
       <c r="A137" t="s">
         <v>1730</v>
       </c>
@@ -25478,7 +25478,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="138" spans="1:45" ht="57">
+    <row r="138" spans="1:45" ht="60">
       <c r="A138" t="s">
         <v>1741</v>
       </c>
@@ -25600,7 +25600,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="139" spans="1:45" ht="42.75">
+    <row r="139" spans="1:45" ht="60">
       <c r="A139" t="s">
         <v>1749</v>
       </c>
@@ -25722,7 +25722,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="140" spans="1:45" ht="42.75">
+    <row r="140" spans="1:45" ht="60">
       <c r="A140" t="s">
         <v>1762</v>
       </c>
@@ -25841,7 +25841,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="141" spans="1:45" ht="71.25">
+    <row r="141" spans="1:45" ht="75">
       <c r="A141" t="s">
         <v>1772</v>
       </c>
@@ -25963,7 +25963,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="142" spans="1:45" ht="71.25">
+    <row r="142" spans="1:45" ht="75">
       <c r="A142" t="s">
         <v>1784</v>
       </c>
@@ -26085,7 +26085,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="143" spans="1:45" ht="57">
+    <row r="143" spans="1:45" ht="60">
       <c r="A143" t="s">
         <v>1797</v>
       </c>
@@ -26207,7 +26207,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="144" spans="1:45" ht="57">
+    <row r="144" spans="1:45" ht="60">
       <c r="A144" t="s">
         <v>1810</v>
       </c>
@@ -26329,7 +26329,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="145" spans="1:45" ht="42.75">
+    <row r="145" spans="1:45" ht="45">
       <c r="A145" t="s">
         <v>1820</v>
       </c>
@@ -26457,7 +26457,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="146" spans="1:45" ht="42.75">
+    <row r="146" spans="1:45" ht="45">
       <c r="A146" t="s">
         <v>1831</v>
       </c>
@@ -26582,7 +26582,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="147" spans="1:45" ht="57">
+    <row r="147" spans="1:45" ht="60">
       <c r="A147" t="s">
         <v>1840</v>
       </c>
@@ -26704,7 +26704,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="148" spans="1:45" ht="57">
+    <row r="148" spans="1:45" ht="60">
       <c r="A148" t="s">
         <v>1848</v>
       </c>
@@ -26826,7 +26826,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="149" spans="1:45" ht="57">
+    <row r="149" spans="1:45" ht="75">
       <c r="A149" t="s">
         <v>1860</v>
       </c>
@@ -26945,7 +26945,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="150" spans="1:45" ht="42.75">
+    <row r="150" spans="1:45" ht="45">
       <c r="A150" t="s">
         <v>1872</v>
       </c>
@@ -27070,7 +27070,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="151" spans="1:45" ht="57">
+    <row r="151" spans="1:45" ht="75">
       <c r="A151" t="s">
         <v>1888</v>
       </c>
@@ -27192,7 +27192,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="152" spans="1:45" ht="57">
+    <row r="152" spans="1:45" ht="75">
       <c r="A152" t="s">
         <v>1901</v>
       </c>
@@ -27308,7 +27308,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="153" spans="1:45" ht="57">
+    <row r="153" spans="1:45" ht="60">
       <c r="A153" t="s">
         <v>1910</v>
       </c>
@@ -27427,7 +27427,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="154" spans="1:45" ht="57">
+    <row r="154" spans="1:45" ht="60">
       <c r="A154" t="s">
         <v>1920</v>
       </c>
@@ -27549,7 +27549,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="155" spans="1:45" ht="42.75">
+    <row r="155" spans="1:45" ht="45">
       <c r="A155" t="s">
         <v>1929</v>
       </c>
@@ -27668,7 +27668,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="156" spans="1:45" ht="57">
+    <row r="156" spans="1:45" ht="60">
       <c r="A156" t="s">
         <v>1939</v>
       </c>
@@ -27784,7 +27784,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="157" spans="1:45" ht="28.5">
+    <row r="157" spans="1:45" ht="45">
       <c r="A157" t="s">
         <v>1951</v>
       </c>
@@ -27900,7 +27900,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="158" spans="1:45" ht="57">
+    <row r="158" spans="1:45" ht="60">
       <c r="A158" t="s">
         <v>1961</v>
       </c>
@@ -28025,7 +28025,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="159" spans="1:45" ht="42.75">
+    <row r="159" spans="1:45" ht="60">
       <c r="A159" t="s">
         <v>1972</v>
       </c>
@@ -28147,7 +28147,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="160" spans="1:45" ht="42.75">
+    <row r="160" spans="1:45" ht="45">
       <c r="A160" t="s">
         <v>1982</v>
       </c>
@@ -28269,7 +28269,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="161" spans="1:45" ht="71.25">
+    <row r="161" spans="1:45" ht="75">
       <c r="A161" t="s">
         <v>1993</v>
       </c>
@@ -28394,7 +28394,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="162" spans="1:45" ht="57">
+    <row r="162" spans="1:45" ht="60">
       <c r="A162" t="s">
         <v>2004</v>
       </c>
@@ -28510,7 +28510,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="163" spans="1:45" ht="42.75">
+    <row r="163" spans="1:45" ht="45">
       <c r="A163" t="s">
         <v>2014</v>
       </c>
@@ -28632,7 +28632,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="164" spans="1:45" ht="57">
+    <row r="164" spans="1:45" ht="75">
       <c r="A164" t="s">
         <v>2020</v>
       </c>
@@ -28757,7 +28757,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="165" spans="1:45" ht="42.75">
+    <row r="165" spans="1:45" ht="75">
       <c r="A165" t="s">
         <v>2032</v>
       </c>
@@ -28879,7 +28879,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="166" spans="1:45" ht="42.75">
+    <row r="166" spans="1:45" ht="45">
       <c r="A166" t="s">
         <v>2044</v>
       </c>
@@ -29001,7 +29001,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="167" spans="1:45" ht="71.25">
+    <row r="167" spans="1:45" ht="90">
       <c r="A167" t="s">
         <v>2055</v>
       </c>
@@ -29123,7 +29123,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="168" spans="1:45" ht="57">
+    <row r="168" spans="1:45" ht="75">
       <c r="A168" t="s">
         <v>2067</v>
       </c>
@@ -29242,7 +29242,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="169" spans="1:45" ht="42.75">
+    <row r="169" spans="1:45" ht="45">
       <c r="A169" t="s">
         <v>2077</v>
       </c>
@@ -29364,7 +29364,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="170" spans="1:45" ht="57">
+    <row r="170" spans="1:45" ht="60">
       <c r="A170" t="s">
         <v>2083</v>
       </c>
@@ -29489,7 +29489,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="171" spans="1:45" ht="42.75">
+    <row r="171" spans="1:45" ht="60">
       <c r="A171" t="s">
         <v>2096</v>
       </c>
@@ -29614,7 +29614,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="172" spans="1:45" ht="42.75">
+    <row r="172" spans="1:45" ht="60">
       <c r="A172" t="s">
         <v>2108</v>
       </c>
@@ -29733,7 +29733,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="173" spans="1:45" ht="71.25">
+    <row r="173" spans="1:45" ht="75">
       <c r="A173" t="s">
         <v>2120</v>
       </c>
@@ -29855,7 +29855,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="174" spans="1:45" ht="42.75">
+    <row r="174" spans="1:45" ht="45">
       <c r="A174" t="s">
         <v>2131</v>
       </c>
@@ -29977,7 +29977,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="175" spans="1:45" ht="57">
+    <row r="175" spans="1:45" ht="60">
       <c r="A175" t="s">
         <v>2141</v>
       </c>
@@ -30093,7 +30093,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="176" spans="1:45" ht="42.75">
+    <row r="176" spans="1:45" ht="60">
       <c r="A176" t="s">
         <v>2152</v>
       </c>
@@ -30215,7 +30215,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="177" spans="1:45" ht="28.5">
+    <row r="177" spans="1:45" ht="30">
       <c r="A177" t="s">
         <v>2164</v>
       </c>
@@ -30331,7 +30331,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="178" spans="1:45" ht="57">
+    <row r="178" spans="1:45" ht="60">
       <c r="A178" t="s">
         <v>2180</v>
       </c>
@@ -30450,7 +30450,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="179" spans="1:45" ht="42.75">
+    <row r="179" spans="1:45" ht="45">
       <c r="A179" t="s">
         <v>2192</v>
       </c>
@@ -30569,7 +30569,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="180" spans="1:45" ht="42.75">
+    <row r="180" spans="1:45" ht="45">
       <c r="A180" t="s">
         <v>2205</v>
       </c>
@@ -30685,7 +30685,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="181" spans="1:45" ht="42.75">
+    <row r="181" spans="1:45" ht="60">
       <c r="A181" t="s">
         <v>2216</v>
       </c>
@@ -30801,7 +30801,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="182" spans="1:45" ht="57">
+    <row r="182" spans="1:45" ht="75">
       <c r="A182" t="s">
         <v>2225</v>
       </c>
@@ -30923,7 +30923,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="183" spans="1:45" ht="57">
+    <row r="183" spans="1:45" ht="90">
       <c r="A183" t="s">
         <v>2239</v>
       </c>
@@ -31045,7 +31045,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="184" spans="1:45" ht="42.75">
+    <row r="184" spans="1:45" ht="45">
       <c r="A184" t="s">
         <v>2253</v>
       </c>
@@ -31167,7 +31167,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="185" spans="1:45" ht="57">
+    <row r="185" spans="1:45" ht="60">
       <c r="A185" t="s">
         <v>2262</v>
       </c>
@@ -31292,7 +31292,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="186" spans="1:45" ht="57">
+    <row r="186" spans="1:45" ht="60">
       <c r="A186" t="s">
         <v>2272</v>
       </c>
@@ -31411,7 +31411,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="187" spans="1:45" ht="42.75">
+    <row r="187" spans="1:45" ht="45">
       <c r="A187" t="s">
         <v>2285</v>
       </c>
@@ -31536,7 +31536,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="188" spans="1:45" ht="85.5">
+    <row r="188" spans="1:45" ht="120">
       <c r="A188" t="s">
         <v>2295</v>
       </c>
@@ -31661,7 +31661,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="189" spans="1:45" ht="42.75">
+    <row r="189" spans="1:45" ht="45">
       <c r="A189" t="s">
         <v>2307</v>
       </c>
@@ -31783,7 +31783,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="190" spans="1:45" ht="57">
+    <row r="190" spans="1:45" ht="60">
       <c r="A190" t="s">
         <v>2320</v>
       </c>
@@ -31902,7 +31902,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="191" spans="1:45" ht="57">
+    <row r="191" spans="1:45" ht="60">
       <c r="A191" t="s">
         <v>2331</v>
       </c>
@@ -32018,7 +32018,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="192" spans="1:45" ht="42.75">
+    <row r="192" spans="1:45" ht="45">
       <c r="A192" t="s">
         <v>2341</v>
       </c>
@@ -32134,7 +32134,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="193" spans="1:45" ht="42.75">
+    <row r="193" spans="1:45" ht="60">
       <c r="A193" t="s">
         <v>2351</v>
       </c>
@@ -32259,7 +32259,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="194" spans="1:45" ht="57">
+    <row r="194" spans="1:45" ht="60">
       <c r="A194" t="s">
         <v>2360</v>
       </c>
@@ -32378,7 +32378,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="195" spans="1:45" ht="42.75">
+    <row r="195" spans="1:45" ht="45">
       <c r="A195" t="s">
         <v>2372</v>
       </c>
@@ -32494,7 +32494,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="196" spans="1:45" ht="57">
+    <row r="196" spans="1:45" ht="75">
       <c r="A196" t="s">
         <v>2386</v>
       </c>
@@ -32610,7 +32610,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="197" spans="1:45" ht="71.25">
+    <row r="197" spans="1:45" ht="75">
       <c r="A197" t="s">
         <v>2398</v>
       </c>
@@ -32732,7 +32732,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="198" spans="1:45" ht="71.25">
+    <row r="198" spans="1:45" ht="75">
       <c r="A198" t="s">
         <v>2411</v>
       </c>
@@ -32848,7 +32848,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="199" spans="1:45" ht="57">
+    <row r="199" spans="1:45" ht="60">
       <c r="A199" t="s">
         <v>2423</v>
       </c>
@@ -32964,7 +32964,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="200" spans="1:45" ht="71.25">
+    <row r="200" spans="1:45" ht="75">
       <c r="A200" t="s">
         <v>2430</v>
       </c>
@@ -33080,7 +33080,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="201" spans="1:45" ht="42.75">
+    <row r="201" spans="1:45" ht="45">
       <c r="A201" t="s">
         <v>2440</v>
       </c>
@@ -33202,7 +33202,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="202" spans="1:45" ht="71.25">
+    <row r="202" spans="1:45" ht="75">
       <c r="A202" t="s">
         <v>2451</v>
       </c>
@@ -33318,7 +33318,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="203" spans="1:45" ht="42.75">
+    <row r="203" spans="1:45" ht="60">
       <c r="A203" t="s">
         <v>2463</v>
       </c>
@@ -33434,7 +33434,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="204" spans="1:45" ht="71.25">
+    <row r="204" spans="1:45" ht="75">
       <c r="A204" t="s">
         <v>2474</v>
       </c>
@@ -33553,7 +33553,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="205" spans="1:45" ht="42.75">
+    <row r="205" spans="1:45" ht="45">
       <c r="A205" t="s">
         <v>2484</v>
       </c>
@@ -33669,7 +33669,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="206" spans="1:45" ht="28.5">
+    <row r="206" spans="1:45" ht="30">
       <c r="A206" t="s">
         <v>2489</v>
       </c>
@@ -33785,7 +33785,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="207" spans="1:45" ht="57">
+    <row r="207" spans="1:45" ht="75">
       <c r="A207" t="s">
         <v>2501</v>
       </c>
@@ -34058,7 +34058,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="hiddenDataSheet"/>
   <dimension ref="A1:BJ12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:62">
       <c r="A1" t="s">
